--- a/_ForDRA/BVSimulationFiles/88.xlsx
+++ b/_ForDRA/BVSimulationFiles/88.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005088105726872246</v>
+        <v>0.01017621145374449</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005150707164386738</v>
+        <v>0.01030141432877348</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005213308601901229</v>
+        <v>0.01042661720380246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005275910039415719</v>
+        <v>0.01055182007883144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000533851147693021</v>
+        <v>0.01067702295386042</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005401112914444702</v>
+        <v>0.0108022258288894</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0005463714351959194</v>
+        <v>0.01092742870391839</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005526315789473684</v>
+        <v>0.01105263157894737</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005588917226988175</v>
+        <v>0.01117783445397635</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005651518664502666</v>
+        <v>0.01130303732900533</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005714120102017158</v>
+        <v>0.01142824020403432</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0005776721539531648</v>
+        <v>0.0115534430790633</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005839322977046139</v>
+        <v>0.01167864595409228</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000590192441456063</v>
+        <v>0.01180384882912126</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005964525852075121</v>
+        <v>0.01192905170415024</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006027127289589613</v>
+        <v>0.01205425457917923</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0006089728727104104</v>
+        <v>0.01217945745420821</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006152330164618595</v>
+        <v>0.01230466032923719</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0006214931602133086</v>
+        <v>0.01242986320426617</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006277533039647578</v>
+        <v>0.01255506607929516</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005088105726872246</v>
+        <v>0.01017621145374449</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005150707164386738</v>
+        <v>0.01030141432877348</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005213308601901229</v>
+        <v>0.01042661720380246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005275910039415719</v>
+        <v>0.01055182007883144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000533851147693021</v>
+        <v>0.01067702295386042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005401112914444702</v>
+        <v>0.0108022258288894</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005463714351959194</v>
+        <v>0.01092742870391839</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005526315789473684</v>
+        <v>0.01105263157894737</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005588917226988175</v>
+        <v>0.01117783445397635</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005651518664502666</v>
+        <v>0.01130303732900533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005714120102017158</v>
+        <v>0.01142824020403432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005776721539531648</v>
+        <v>0.0115534430790633</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005839322977046139</v>
+        <v>0.01167864595409228</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000590192441456063</v>
+        <v>0.01180384882912126</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005964525852075121</v>
+        <v>0.01192905170415024</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006027127289589613</v>
+        <v>0.01205425457917923</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006089728727104104</v>
+        <v>0.01217945745420821</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006152330164618595</v>
+        <v>0.01230466032923719</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006214931602133086</v>
+        <v>0.01242986320426617</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006277533039647578</v>
+        <v>0.01255506607929516</v>
       </c>
     </row>
   </sheetData>
